--- a/note/data_reference.xlsx
+++ b/note/data_reference.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Healthy Overview" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,16 +12,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Patient Sessions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -31,13 +30,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
+      <color rgb="FF1F4E79"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -47,11 +46,30 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00CC0000"/>
+      <color rgb="FFCC0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFCC0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,16 +78,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
+        <fgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -79,28 +103,80 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="FFB0B0B0"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="FFB0B0B0"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="FFB0B0B0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B0B0"/>
+        <color rgb="FFB0B0B0"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -111,9 +187,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -477,532 +572,533 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>RECORDING PARAMETERS</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
+      <c r="H1" s="13" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Subjects</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>26 healthy (SUB_01–SUB_26), data collection ongoing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>28 healthy (SUB_01–SUB_28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Sessions per subject</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>1–2</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Paradigm</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>AO+MI: Subject imagines walking while watching Walker actually walk</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Trials per session</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>150 total = 60 imagine + 60 walk + 30 rest (30 cycles × 5)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Session duration</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>~57 min continuous recording</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="25" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>EEG</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>actiCHamp, 63ch + FCz ref, 1000Hz, BrainVision format</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Goniometer</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Biometrics Ltd, 1000Hz, 23ch + 1 Stim = 24ch, UTF-16LE .txt</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Goni receivers</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>3 DataLITE receivers × 8ch each; two configs (Type A/B) swap one channel</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>EEG-Goni sync</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>IOI cross-correlation of marker onset times (no periodic S10 triggers)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Alignment residual</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>&lt; 50ms across all 13 sessions verified</t>
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>EEG MARKERS — STANDARD (12/13 sessions)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="13" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>EEG Marker</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>PyLog equivalent</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>S 11</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Experiment START</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>S11</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>S 12</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Experiment END</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>S12</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="E17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="37.5" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>S 1</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Imagine trial START</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>S1 (backward) + S6 (forward)</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Odd/even direction collapsed into same marker</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>S 2</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Imagine trial STOP</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>S2 + S7</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="E19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="37.5" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>S 4</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Walk trial START</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>S4 (forward) + S8 (backward)</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Odd/even direction collapsed into same marker</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>S 5</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Walk trial STOP</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>S5 + S9</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
+      <c r="E21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>S 7</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Rest START</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>S20</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr"/>
+      <c r="E22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>S 8</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Rest STOP</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>S21</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="E23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="37.5" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>TOTAL markers/session</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Must match goni Stim onset count for alignment</t>
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>GONIOMETER — TWO RECEIVER CONFIGS</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="13" t="n"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Config</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>Sessions (7+6=13)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>Missing channel</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>Present instead</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Subject X (6 joints)</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>Walker X</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Type A</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>SUB_01_s01, 02_s01, 02_s02,
 03_s01, 04, 05, 06_s01</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>LAnkW X</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>LAnkS Y</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>All 6 ✓</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>5 only (no LAnk)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="29" ht="25" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Type B</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>SUB_01_s02, 03_s02, 06_s02,
 07, 08, 09</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>LAnkS Y</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>LAnkW X</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>All 6 ✓</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>All 6 ✓</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="30" ht="14.5" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>⚠ Channel column ORDER varies per subject (e.g. SUB_09 completely different). NEVER hardcode indices → use find_goni_idx.m</t>
         </is>
@@ -1024,1916 +1120,2225 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="6" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ALL HEALTHY SESSIONS — from Goni QC v3 + recording logs</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
+      <c r="H1" s="12" t="n"/>
+      <c r="I1" s="13" t="n"/>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Goni file(s)</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Total trials</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>MI</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Walk</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Rest</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Goni problems</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Status / Notes</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SUB_01</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E3" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G3" s="4" t="n">
+      <c r="E3" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Clean. Old experiment script: no S7/S8, rest = R1+S4→R1+S5, 2× S11. Trial extraction needs special handling.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SUB_01</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="E4" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SUB_02</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="E5" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SUB_02</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="E6" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SUB_03</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G7" s="4" t="n">
+      <c r="E7" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>SUB_03</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G8" s="4" t="n">
+      <c r="E8" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>SUB_04</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="E9" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="25" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>SUB_04</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2 files (split!)</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>36+115=151</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G10" s="4" t="n">
+      <c r="F10" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G10" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Recording interrupted → restarted. Two separate goni files (36 trials then 115 trials). Must load and merge both. Trial counts: segment1=36, segment2=115.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SUB_05</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G11" s="4" t="n">
+      <c r="E11" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>SUB_06</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E12" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G12" s="4" t="n">
+      <c r="E12" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>SUB_06</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G13" s="4" t="n">
+      <c r="E13" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Clean. (v2 QC flagged trial 6, v3 reclassified as OK)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>SUB_07</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G14" s="4" t="n">
+      <c r="E14" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>SUB_07</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E15" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G15" s="4" t="n">
+      <c r="E15" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G15" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>SUB_08</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E16" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G16" s="4" t="n">
+      <c r="E16" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>SUB_09</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E17" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G17" s="4" t="n">
+      <c r="E17" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Clean. NOTE: goni channel column order completely different from all other subjects.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="25" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>SUB_09</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>2 files (split!)</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>15+140=155</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>6+56</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>6+56</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>3+28</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Recording interrupted → restarted. Two goni files (15 then 140 trials). Must load and merge both.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="19" ht="25" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>SUB_10</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>1 file (partial?)</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Only 20 trials recorded (likely equipment issue early in session). Segment 2 data unclear.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>SUB_10</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E20" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G20" s="4" t="n">
+      <c r="E20" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G20" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>SUB_11</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E21" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G21" s="4" t="n">
+      <c r="E21" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22" ht="39" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>SUB_12</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>2 files (split!)</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>78+75=153</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>32+30</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>31+30</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>15+15</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>19+19=38</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>SEVERE: Walker goniometer wireless disconnection → zero readings in many trials. 38 trials affected across both segments. Recording also split into 2 goni files.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>SUB_12</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E23" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G23" s="4" t="n">
+      <c r="E23" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G23" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>SUB_13</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="E24" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G24" s="6" t="n">
+      <c r="E24" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="G24" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>MODERATE: 9 trials with goni zeros (wireless disconnection). Exclude affected trials.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>SUB_14</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E25" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G25" s="4" t="n">
+      <c r="E25" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G25" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>v3 QC: 0 real problems (v2 had flagged 25 but reclassified as expected flat readings during rest/stand).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>SUB_15</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E26" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G26" s="4" t="n">
+      <c r="E26" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>SUB_15</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>sess02</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E27" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G27" s="4" t="n">
+      <c r="E27" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G27" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28" ht="25" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>SUB_16</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>2 files (split!)</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>113+40=153</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>46+16</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>45+16</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>22+8</t>
         </is>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="4" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Recording interrupted → restarted. Two goni files (113 then 40 trials). Must load and merge both.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>SUB_17</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E29" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G29" s="4" t="n">
+      <c r="E29" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G29" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>SUB_18</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G30" s="4" t="n">
+      <c r="F30" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Clean. 149 trials (1 trial lost, likely marker issue).</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>SUB_19</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="E31" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G31" s="4" t="n">
+      <c r="E31" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="4" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Clean.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>SUB_20</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>1 file</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SUB_21</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>1 file</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>V8 processed (10 bad ch). Earlier QC flagged 19/60 GI trials with Walker goni zeros. Needs goni re-QC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="39" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SUB_22</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>3 files (split!)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>78+3+70</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>SEVERE: Goni wireless disconnect → mid-session restart → 3 recording segments. Segment 2 (3 trials) has NO corresponding EEG S11 marker. Visual alignment done by Neethu. Custom loading script needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="25" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SUB_23</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>1 file</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Clean. V8 processed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SUB_24</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1 file</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>150</v>
+      </c>
+      <c r="E36" t="n">
+        <v>60</v>
+      </c>
+      <c r="F36" t="n">
+        <v>60</v>
+      </c>
+      <c r="G36" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Clean. V8 processed. Only mixed-gender pair (female subject, male walker).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SUB_25</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1 file</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>150</v>
+      </c>
+      <c r="E37" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" t="n">
+        <v>60</v>
+      </c>
+      <c r="G37" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Clean. V8 processed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SUB_26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1 file</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>150</v>
+      </c>
+      <c r="E38" t="n">
+        <v>60</v>
+      </c>
+      <c r="F38" t="n">
+        <v>60</v>
+      </c>
+      <c r="G38" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>V8: 11 bad ch (entire frontal strip). Processed with warning. Needs extra scrutiny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SUB_27</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1 file</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>150</v>
+      </c>
+      <c r="E39" t="n">
+        <v>60</v>
+      </c>
+      <c r="F39" t="n">
+        <v>60</v>
+      </c>
+      <c r="G39" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Clean. V8 processed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SUB_28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3 files (split!)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>NEW: 3 recording blocks. EEG not yet V8 processed (multi-file, needs merge). Goni QC pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>SPLIT SESSION DETAIL — sessions where 1 recording became 2+ files</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="12" t="n"/>
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="13" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>Goni filename (timestamp)</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Trials</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>Walk</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>Why split / What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SUB_04</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>sess02</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>1 of 2</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11Mar2026-141250.957</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Recording interrupted (unknown cause). Load as separate .mat, align independently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>SUB_04</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>sess02</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>2 of 2</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11Mar2026-143125.403</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Main segment. Merge both for full session.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SUB_09</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>sess02</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>1 of 2</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>23Mar2026-135433.557</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Recording interrupted. Short first segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SUB_09</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>sess02</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2 of 2</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>23Mar2026-142441.410</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Main segment. Merge both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>SUB_10</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>1 of 2?</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>06Mar2026-140341.688</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Only 20 trials. Possible second segment not yet documented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>SUB_12</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>1 of 2</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>17Mar2026-105800.701</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Both segments have Walker goni zeros (19 problems each). Wireless disconnect persisted across restart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="25" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>SUB_12</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>2 of 2</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>17Mar2026-112420.855</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Same goni issue continues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>SUB_16</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>1 of 2</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>18Mar2026-135057.650</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Recording interrupted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>SUB_16</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2 of 2</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>18Mar2026-143726.758</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Shorter second segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>SUB_22</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>1 of 3</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>30Mar2026-153954.902</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>Not in QC v3 output. Data status unclear.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>SUB_21</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Normal first segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SUB_22</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>2 of 3</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>30Mar2026-161720.228 (file 1)</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>PROBLEM: No EEG S11 for this segment. No automatic alignment possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>SUB_22</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>sess01</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>3 of 3</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>30Mar2026-161720.228 (file 2)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Not in QC v3. Earlier QC flagged 19/60 GI trials with Walker goni zeros.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>SUB_22</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>SEVERE: 3 recording segments. Goni wireless disconnect → mid-session restart. Segment 2 (3 trials) has NO EEG S11. Visual alignment by Neethu. EEG not yet V8 processed (multi-file, needs merge).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SUB_28</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>3 files (split!)</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>78+3+70</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>SEVERE: Goni wireless disconnect → mid-session restart → 3 recording segments. Segment 2 (3 trials) has NO corresponding EEG S11 marker. Visual alignment done by Neethu. Custom loading script needed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>SUB_23–26</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>Not yet in QC. Data collection ongoing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>SPLIT SESSION DETAIL — sessions where 1 recording became 2+ files</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>Session</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Segment</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Goni filename (timestamp)</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Trials</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>MI</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>Walk</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Rest</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>Why split / What to do</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>SUB_04</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>sess02</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>1 of 2</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>11Mar2026-141250.957</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>Recording interrupted (unknown cause). Load as separate .mat, align independently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>SUB_04</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>sess02</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>2 of 2</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>11Mar2026-143125.403</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>Main segment. Merge both for full session.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>SUB_09</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>sess02</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>1 of 2</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>23Mar2026-135433.557</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>Recording interrupted. Short first segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>SUB_09</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>sess02</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>2 of 2</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>23Mar2026-142441.410</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>Main segment. Merge both.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>SUB_10</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1 of 3</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>07Apr2026-155122.402</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Block 1. Standard first segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SUB_28</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>1 of 2?</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>06Mar2026-140341.688</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Only 20 trials. Possible second segment not yet documented.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>SUB_12</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2 of 3</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>07Apr2026-164148.666</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Block 2. Possibly short segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SUB_28</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>sess01</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>1 of 2</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>17Mar2026-105800.701</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="n">
-        <v>78</v>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>Both segments have Walker goni zeros (19 problems each). Wireless disconnect persisted across restart.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>SUB_12</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>sess01</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>2 of 2</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>17Mar2026-112420.855</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>Same goni issue continues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>SUB_16</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>sess01</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>1 of 2</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>18Mar2026-135057.650</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>Recording interrupted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>SUB_16</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>sess01</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>2 of 2</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>18Mar2026-143726.758</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>Shorter second segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>SUB_22</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>sess01</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>1 of 3</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>30Mar2026-153954.902</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>Normal first segment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>SUB_22</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>sess01</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>2 of 3</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>30Mar2026-161720.228 (file 1)</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F49" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>PROBLEM: No EEG S11 for this segment. No automatic alignment possible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>SUB_22</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>sess01</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>3 of 3</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>30Mar2026-161720.228 (file 2)</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>Neethu created duplicate dir with visual alignment. Custom loading script: data_load_eeg_pilot_feb2026_sub22_sess1.m</t>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>07Apr2026-165711.346</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Block 3. Trial counts TBD.</t>
         </is>
       </c>
     </row>
@@ -2952,584 +3357,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>PARTICIPANTS</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
+      <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Subject</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Diagnosis</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Stim OFF</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Stim ON</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Sub01</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>RESTORE2_001 (Mr. Chong)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>SCI, epidural SCS</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>5 (Sess01–05)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Sess01–03</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Sess04–05</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>YOB 1966, Cap 56</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Sub02</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>RESTORE2_002 (Ms. Stella)</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>SCI, epidural SCS</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>3 + Resting</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Sess01</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Sess02–03</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cap 56. Resting state recorded to characterize stim ON/OFF artifacts.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>RECORDING PARAMETERS</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="B6" s="12" t="n"/>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="13" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Parameter</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>EEG</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>actiCHamp Plus, 63ch + Cz ref (differs from healthy FCz), 1000Hz, BrainVision format</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="62.5" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>GI paradigm</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Patient seated, imagines walking while watching Walker walk. 20–55 trials/session (variable by fatigue).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Session flow</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>S2S(×5) → GI Block 1 → [6m Walk + GI]×2 → GI Block 2 → 2-min Walk → GI Block 3</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>EEG-Goni sync</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>S10 periodic sync pulses (83–144/session) matched to Goni Stim channel rising edges</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="25" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Alignment quality</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Max error 43ms across all sessions. &gt;99% match rate.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>EEG MARKERS — STANDARD (Sess03 onward)</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="13" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>EEG Marker</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>Count/session</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>S 10</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Periodic sync trigger</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>83–144</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>For alignment ONLY. Not an experiment event. Sent to both EEG and Goni simultaneously.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>S 11</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Experiment START</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Absent in Sess01–02 (legacy protocol).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>S 12</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Experiment END</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Absent in Sess01–02; also missing in Sub02_Sess03.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>S 1 / S 2</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>GI START / END</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>20–55</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Main analysis target.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>S 3 / R 1</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>6m Walk START / END</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Walker walks, patient watches.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>S 4 / S 5</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Sit-to-Stand START / END</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>5–6</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Patient performs actual movement.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>S 7 / S 8</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>2-Min Walk START / END</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>0–1</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Patient walks with FLOAT support. Only 3 usable segments across all 8 sessions.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>S 6, S20/21</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Relax break</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Alternative naming for rest periods.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>LEGACY MARKERS — Sub01 Sess01–02 only (before 22 Dec 2025)</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="13" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>Standard meaning (Sess03+)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>Legacy meaning (Sess01–02)</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>S 1</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>GI START</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Eyes Close / Imagine Start</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>In files 0009–0012 (Sess01), S1/S2 still appear to mean GI despite legacy protocol.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>S 3</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>6m Walk START</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>6m Walk START</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Same meaning, different context.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>S 7 / S 8</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>2-Min Walk START/END</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>2-Min Walk START/END</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Same meaning.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>S 13 / S 14</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>(not used)</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>6MW Pause / Resume</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Only in legacy sessions.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>S 11 / S 12</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Experiment START/END</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>(absent)</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Cannot auto-trim. Use skip_trim=true or S10 bookends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>bad data</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Sub01</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>SESSION3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>SESSION4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Sub02</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>SESSION1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>SESSION2</t>
         </is>
       </c>
     </row>
@@ -3550,14 +3998,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -3566,122 +4013,122 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ALL PATIENT SESSIONS — detailed</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
+      <c r="H1" s="12" t="n"/>
+      <c r="I1" s="12" t="n"/>
+      <c r="J1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Stim</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>EEG files</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Goni files</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>GI trials</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>S2S</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>2MW</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Issues</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Handling</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Sub01
 Sess01</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>30 Oct
 2025</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>6 files
 (0001,0008–0012)</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Multiple
 (per EEG file)</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>51
 (from 0009–0012)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>5
 (in 0008)</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>1 usable
 (2486–2608s)</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Legacy markers (no S11/S12).
 0001: only goni trigger, no EEG data → discard.
@@ -3689,7 +4136,7 @@
 0010: USB error during recording.</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>pop_mergeset files 0009–0012 only.
 skip_trim=true.
@@ -3697,109 +4144,109 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4" ht="37.5" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Sub01
 Sess02</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>13 Nov
 2025</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>3 files
 (0013–0015)</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>3 goni files</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>~53
 (18+18+17)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Legacy markers (no S11/S12).
 Shoulder movement during Block 2 GI → possible motor artifact.</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>pop_mergeset all 3.
 skip_trim=true.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Sub01
 Sess03</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>22 Dec
 2025</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>2 goni files
 (goni restarted)</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>~29</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Bad REF electrode (Cz impedance &gt;20kΩ) → corrupts ALL channels.
 clean_rawdata flags 16–38/63 channels.
@@ -3807,60 +4254,65 @@
 Goni restarted mid-session → 2 files (59+44 stim vs 103 S10).</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>SESSION ABANDONED — do not use for analysis.
 If used: align each goni file separately.</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62.5" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sub01
 Sess04</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>20 Jan
 2026</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2 files
 (0016, 0018)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>2 goni files</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>27
 (13+14 in 0016)</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>5
 (in 0018)</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Bad REF electrode (elevated bad channels).
 Goni wireless disconnect → gap at 335–775s in file 1, 1 stim trigger lost.
@@ -3868,299 +4320,314 @@
 First session with stim ON → eSCS EM artifact in EEG.</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>pop_mergeset both files.
 Alignment fallback (brute-force) works → 82/83 matched.
 Process with caution (bad REF + stim artifact).</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Sub01
 Sess05</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>20 Feb
 2026</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>1 file
 (0020)</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>1 goni file</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>~45</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Partial
 (49s only)</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Stim ON (eSCS artifact present).
 2MW: S7 sent but recording ended (S12) before S8 → only 49s of walk.
 Patient exhausted during 6m walk, only half a rep.</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Standard processing.
 2MW segment too short to use.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="39" customFormat="1" customHeight="1" s="9">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sub02
 Sess01</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>05 Jan
 2026</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>1 goni file</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>29
 (14+15)</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>1 usable
 (S7+120s)</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Bad REF electrode (Cz &gt;20kΩ, elevated bad ch).
 FLOAT battery running out → only 2 GI blocks.
 Second S7: only 13s before S12 → not usable.</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Process with caution (bad REF).
 2MW: use S7 + 120s as end time.</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="39" customFormat="1" customHeight="1" s="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sub02
 Sess02</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>29 Jan
 2026</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>1 file
 (0018)</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>1 goni file</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>39
 (13+13+13)</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>1 usable
 (S7+120s)</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Bad REF electrode (Cz &gt;20kΩ, elevated bad ch).
 Different FLOAT weight percentages (90/70/50/20%) for S2S.</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>Process with caution (bad REF).
 2MW: use S7 + 120s as end time.</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="37.5" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sub02
 Sess03</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>02 Mar
 2026</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1 goni file</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>S11 present but NO S12 marker → cannot auto-trim end.
 1 spurious stim pulse at goni end (145 vs 144 S10).
 Stronger eSCS stimulation parameters in this session.</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Trim from S11 to end-of-recording.
 Alignment: last goni stim ignored (spurious).</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Sub02
 Sess04</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>(later)</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>ON
 (stronger)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>1 file</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>1 goni file</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>SEVERE: clean_rawdata at corr=0.8 flags 33/59 channels as bad.
 Root cause: stronger eSCS stimulation parameters → EM artifact overwhelms scalp EEG.
 corr=0.7 → 11 bad; corr=0.6 → 3 bad.</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Requires relaxed threshold (corr=0.6 or 0.7)
 or exclusion from group analysis.</t>
@@ -4168,748 +4635,798 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>ALIGNMENT QUALITY — S10 ↔ Goni Stim matching</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="13" t="n"/>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>S10 count</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>Goni Stim count</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>Matched</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Max timing error</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>Match rate</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="37.5" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Sub01 Sess01 (6 EEG files)</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>43ms</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="G15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="37.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Sub01 Sess02 (3 EEG files)</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>43ms</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="G16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="39" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Sub01 Sess03 — Goni file 1</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Goni restarted mid-session → fewer stim onsets than S10</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Sub01 Sess03 — Goni file 2</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Second goni file covers rest of session</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Sub01 Sess04 — EEG file 1</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Goni gap 335–775s → 1 stim trigger missing in gap</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Sub01 Sess04 — EEG file 2</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>41ms</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Sub01 Sess05</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>41ms</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="G21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="39" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Sub02 Sess01</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>41ms</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Higher S10 frequency (144 vs 83)</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="39" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Sub02 Sess02</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>41ms</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Sub02 Sess03</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1 spurious stim pulse at very end of goni recording</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>2-MIN WALK (S7→S8) USABILITY</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="13" t="n"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>S7 events</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>S8 events</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>Usable?</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>Why / How</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28" ht="112.5" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Sub01 Sess01</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>~122s (2486–2608s)</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Complete S7→S8 pair. Only session with actual S8 marker.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29" ht="169" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Sub01 Sess03</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>~20s each</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>These S7 markers are individual short walk trials, not 2-min continuous walk.</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="117" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Sub01 Sess05</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>49s (S7 to S12)</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Walk started but recording ended (S12) before 2 minutes elapsed.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="31" ht="112.5" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Sub02 Sess01 (1st S7)</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>~120s (2050–2170s)</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>No S8 sent. Use S7 + 120s as endpoint (standard 2-min walk).</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="91" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Sub02 Sess01 (2nd S7)</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>13s (to S12)</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Only 13 seconds of data before recording ended.</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="75" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Sub02 Sess02</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>~120s (2253–2373s)</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>No S8 sent. Use S7 + 120s as endpoint.</t>
         </is>
       </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>bad data,excluded</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>RESTING STATE (Sub02 only) — separate recording, no gait markers</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>Segment</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>Start marker</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>End marker</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>Eyes</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="1" t="inlineStr">
         <is>
           <t>Stim</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
+      <c r="A37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>eye_open_stim_off (66s)</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>stop (189s)</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>~122s</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Baseline condition</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>eye_close_stim_off (213s)</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>stop (330s)</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>~117s</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr"/>
+      <c r="G38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
+      <c r="A39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>eye_open_stim_on (960s)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>stop (1081s)</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>~121s</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>For stim artifact characterization</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>eye_close_stim_on (1100s)</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>stop (1218s)</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>~119s</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>ON</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr"/>
+      <c r="G40" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
